--- a/SGC-CKN/Excel/cf91a6dd-1cbd-483e-8492-74be820e2cf0_Hạng_mục__Thi_công_cọc_khoan_nhồi__tường_vây_cho_các_hạng_mục_Lô_CT-02_P11-129_D800_03-04-2026.xlsx
+++ b/SGC-CKN/Excel/cf91a6dd-1cbd-483e-8492-74be820e2cf0_Hạng_mục__Thi_công_cọc_khoan_nhồi__tường_vây_cho_các_hạng_mục_Lô_CT-02_P11-129_D800_03-04-2026.xlsx
@@ -1158,7 +1158,7 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <v>-3.5</v>
@@ -1167,10 +1167,10 @@
         <v>1</v>
       </c>
       <c r="I11" s="5">
-        <v>2.79</v>
+        <v>3.5</v>
       </c>
       <c r="J11" s="8">
-        <v>2.79</v>
+        <v>3.5</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1371,16 +1371,16 @@
         <v>-38.4</v>
       </c>
       <c r="G17" s="25">
-        <v>-41.7</v>
+        <v>-44.7</v>
       </c>
       <c r="H17" s="25">
         <v>0.85</v>
       </c>
       <c r="I17" s="25">
-        <v>3.3</v>
-      </c>
-      <c r="J17" s="8">
-        <v>3.88</v>
+        <v>6.3</v>
+      </c>
+      <c r="J17" s="12">
+        <v>7.41</v>
       </c>
       <c r="K17" s="26" t="s">
         <v>51</v>
@@ -1403,19 +1403,19 @@
         <v>54</v>
       </c>
       <c r="F18" s="28">
-        <v>-41.7</v>
+        <v>-44.7</v>
       </c>
       <c r="G18" s="28">
-        <v>-49.95</v>
+        <v>-49.93</v>
       </c>
       <c r="H18" s="28">
         <v>2.95</v>
       </c>
       <c r="I18" s="28">
-        <v>8.25</v>
+        <v>5.23</v>
       </c>
       <c r="J18" s="8">
-        <v>2.8</v>
+        <v>1.77</v>
       </c>
       <c r="K18" s="29" t="s">
         <v>55</v>
@@ -1570,7 +1570,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>-3.5</v>
@@ -1579,10 +1579,10 @@
         <v>1</v>
       </c>
       <c r="H2" s="5">
-        <v>2.79</v>
+        <v>3.5</v>
       </c>
       <c r="I2" s="8">
-        <v>2.79</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1747,16 +1747,16 @@
         <v>-38.4</v>
       </c>
       <c r="F8" s="25">
-        <v>-41.7</v>
+        <v>-44.7</v>
       </c>
       <c r="G8" s="25">
         <v>0.85</v>
       </c>
       <c r="H8" s="25">
-        <v>3.3</v>
-      </c>
-      <c r="I8" s="8">
-        <v>3.88</v>
+        <v>6.3</v>
+      </c>
+      <c r="I8" s="12">
+        <v>7.41</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1773,19 +1773,19 @@
         <v>1</v>
       </c>
       <c r="E9" s="28">
-        <v>-41.7</v>
+        <v>-44.7</v>
       </c>
       <c r="F9" s="28">
-        <v>-49.95</v>
+        <v>-49.93</v>
       </c>
       <c r="G9" s="28">
         <v>2.95</v>
       </c>
       <c r="H9" s="28">
-        <v>8.25</v>
+        <v>5.23</v>
       </c>
       <c r="I9" s="8">
-        <v>2.8</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1802,19 +1802,19 @@
         <v>8</v>
       </c>
       <c r="E10" s="33">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="F10" s="33">
-        <v>-49.95</v>
+        <v>-49.93</v>
       </c>
       <c r="G10" s="33">
         <v>7.8</v>
       </c>
       <c r="H10" s="33">
-        <v>49.24</v>
+        <v>49.93</v>
       </c>
       <c r="I10" s="33">
-        <v>6.31</v>
+        <v>6.4</v>
       </c>
     </row>
   </sheetData>
